--- a/order_forms/048_drive_thru_meal_order_form--order_forms.xlsx
+++ b/order_forms/048_drive_thru_meal_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,8 +750,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,12 +779,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'pickup_window',_'value':_'pickup_window'}</t>
+          <t>pickup_window</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Pickup Window', 'value': 'Pickup Window'}</t>
+          <t>Pickup Window</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'drivethru',_'value':_'drivethru'}</t>
+          <t>drivethru</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'DriveThru', 'value': 'DriveThru'}</t>
+          <t>DriveThru</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'delivery',_'value':_'delivery'}</t>
+          <t>delivery</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Delivery', 'value': 'Delivery'}</t>
+          <t>Delivery</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'curbside',_'value':_'curbside'}</t>
+          <t>curbside</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Curbside', 'value': 'Curbside'}</t>
+          <t>Curbside</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'hamburger',_'value':_'hamburger'}</t>
+          <t>hamburger</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Hamburger', 'value': 'Hamburger'}</t>
+          <t>Hamburger</t>
         </is>
       </c>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'fries',_'value':_'fries'}</t>
+          <t>fries</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Fries', 'value': 'Fries'}</t>
+          <t>Fries</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'sandwich',_'value':_'sandwich'}</t>
+          <t>sandwich</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Sandwich', 'value': 'Sandwich'}</t>
+          <t>Sandwich</t>
         </is>
       </c>
     </row>
